--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251119_201629.xlsx
@@ -4492,7 +4492,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5116,7 +5116,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7498,7 +7498,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
